--- a/output/food_report.xlsx
+++ b/output/food_report.xlsx
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>172.62</v>
+        <v>1028.81</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43.155</v>
+        <v>54.1478947368421</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.246</v>
+        <v>0.1824568827923997</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -575,45 +575,77 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>125.83</v>
+        <v>768.49</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>62.915</v>
+        <v>64.04083333333334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cafe</t>
+          <t>Fine Dining</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39.18</v>
+        <v>179.94</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>39.18</v>
+        <v>179.94</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>50.22</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>25.11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Fast Food</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>7.61</v>
+      <c r="C6" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5.35</v>
       </c>
     </row>
   </sheetData>
@@ -627,10 +659,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -665,44 +697,124 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>125.83</v>
+        <v>450.2</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>62.915</v>
+        <v>75.03333333333333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>39.18</v>
+        <v>247.29</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>39.18</v>
+        <v>123.645</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>125.33</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>31.3325</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Italian</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>76.34</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>38.17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Other Asian</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>31.025</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>35.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Latin American</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>24.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Mexican</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C9" s="2" t="n">
         <v>7.61</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D9" s="2" t="n">
         <v>7.61</v>
       </c>
     </row>
@@ -717,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -744,24 +856,68 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>108.43</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>172.86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>2016</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>75.22999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>64.19</v>
+      <c r="C5" s="2" t="n">
+        <v>185.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>394.88</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>128.33</v>
       </c>
     </row>
   </sheetData>
@@ -775,23 +931,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="41" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="6" customWidth="1" min="15" max="15"/>
     <col width="7" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1134,6 +1290,988 @@
       </c>
       <c r="P5" t="n">
         <v>2016</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2019-02-19</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chef Wang</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Chinese</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Scallion pancake pork buns beef</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="n">
+        <v>35.52</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2016-04-24</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Umix</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paris and Le Classique</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2012-04-27</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>In-N-Out Burger</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hamburger</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2012-05-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grotto Pizzeria and Tavern</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Italian</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pizza salad beer and bread</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="n">
+        <v>45.58</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Year inferred from printed date</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2019-07-26</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Deccan Spice</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Other Asian</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dal fry paneer masala biryani rice</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2018-07-13</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hawwi Ethiopian Restau</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ethiopian fish goulash dullet vegetarian dish</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="n">
+        <v>69.76000000000001</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Merchant name appears truncated on receipt</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2017-04-20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>El Gran Mar de Plata</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bar</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Miller Lite beer</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2019-05-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Golden Bowl Teriyaki</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fast Food</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Other Asian</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Chicken plate avocado drink</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>13</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>R013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2017-08-15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Saska's</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Fine Dining</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ribeye steak lobster sirloin cocktails</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>167</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="n">
+        <v>179.94</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>14</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2018-06-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Akira</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hibachi steak noodle sushi rolls</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Date partially legible</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>15</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2018-05-11</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Katana Sushi</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Hamachi poke bowl sashimi salmon</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>153.71</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Handwritten total suggests 10.00 tip</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>16</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dona Mercedes Restaurant</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Latin American</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Chicharron pupusa platanos quesadilla</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Date not shown</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>17</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2019-08-09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Bella Pasta</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Italian</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Steak tip skewers gorgonzola beer</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>28.48</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="n">
+        <v>30.76</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>18</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2018-07-21</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Friendly Red's of Windham</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Margaritas crab cakes chicken sandwich beer</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="n">
+        <v>77.83</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>19</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2015-06-26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Quick 73</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Casual Dining</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beef ribs pulled pork corn macaroni</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Card</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Year inferred from abbreviated date</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>20</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>
@@ -1147,13 +2285,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1184,6 +2322,181 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R008</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Confidence is medium: Year inferred from printed date</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R010</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Confidence is medium: Merchant name appears truncated on receipt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R014</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Confidence is medium: Date partially legible</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R015</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Confidence is medium: Handwritten total suggests 10.00 tip</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Date is missing, so this row is left out of anything grouped by year</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R016</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Confidence is low: Date not shown</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R019</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Confidence is medium: Year inferred from abbreviated date</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
